--- a/data/wardname.xlsx
+++ b/data/wardname.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\GitHub\discrete_choice\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{84016C36-911C-41C1-99E0-34590406C3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F3847B6-0161-4379-A816-9FDF7AF68F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{E2C4C336-0B01-4DA2-BC3F-5158D1476CC2}"/>
+    <workbookView xWindow="0" yWindow="1164" windowWidth="9180" windowHeight="12024" activeTab="1" xr2:uid="{E2C4C336-0B01-4DA2-BC3F-5158D1476CC2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="76">
   <si>
     <t>00AEGJ : Alperton</t>
   </si>
@@ -162,6 +163,108 @@
   </si>
   <si>
     <t>Willesden Green</t>
+  </si>
+  <si>
+    <t>barking_and_dagenham</t>
+  </si>
+  <si>
+    <t>barnet</t>
+  </si>
+  <si>
+    <t>bexley</t>
+  </si>
+  <si>
+    <t>brent</t>
+  </si>
+  <si>
+    <t>bromley</t>
+  </si>
+  <si>
+    <t>camden</t>
+  </si>
+  <si>
+    <t>city_of_london</t>
+  </si>
+  <si>
+    <t>croydon</t>
+  </si>
+  <si>
+    <t>ealing</t>
+  </si>
+  <si>
+    <t>enfield</t>
+  </si>
+  <si>
+    <t>greenwich</t>
+  </si>
+  <si>
+    <t>hackney</t>
+  </si>
+  <si>
+    <t>hammersmith_and_fulham</t>
+  </si>
+  <si>
+    <t>haringey</t>
+  </si>
+  <si>
+    <t>harrow</t>
+  </si>
+  <si>
+    <t>havering</t>
+  </si>
+  <si>
+    <t>hillingdon</t>
+  </si>
+  <si>
+    <t>hounslow</t>
+  </si>
+  <si>
+    <t>islington</t>
+  </si>
+  <si>
+    <t>kensington_and_chelsea</t>
+  </si>
+  <si>
+    <t>kingston_upon_thames</t>
+  </si>
+  <si>
+    <t>lambeth</t>
+  </si>
+  <si>
+    <t>lewisham</t>
+  </si>
+  <si>
+    <t>merton</t>
+  </si>
+  <si>
+    <t>newham</t>
+  </si>
+  <si>
+    <t>redbridge</t>
+  </si>
+  <si>
+    <t>richmond_upon_thames</t>
+  </si>
+  <si>
+    <t>southwark</t>
+  </si>
+  <si>
+    <t>sutton</t>
+  </si>
+  <si>
+    <t>tower_hamlets</t>
+  </si>
+  <si>
+    <t>waltham_forest</t>
+  </si>
+  <si>
+    <t>wandsworth</t>
+  </si>
+  <si>
+    <t>westminster</t>
+  </si>
+  <si>
+    <t>city_of_london_westminster</t>
   </si>
 </sst>
 </file>
@@ -731,4 +834,385 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0AC5BC7-A737-4F0F-9BD3-0FB43C1C0916}">
+  <dimension ref="A1:C34"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="3" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>2001</v>
+      </c>
+      <c r="B1">
+        <v>2011</v>
+      </c>
+      <c r="C1">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B32" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>